--- a/Motorcycle-Price-All-Models.xlsx
+++ b/Motorcycle-Price-All-Models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819A65C3-FC16-49A5-A0BB-3673DF9405D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7822A7-DDF6-46E7-A6AC-F61E1E7CBBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2AA7A42A-5189-4EA1-AE67-FD5CC8988654}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{2AA7A42A-5189-4EA1-AE67-FD5CC8988654}"/>
   </bookViews>
   <sheets>
     <sheet name="ราคารถทั้งหมด " sheetId="1" r:id="rId1"/>

--- a/Motorcycle-Price-All-Models.xlsx
+++ b/Motorcycle-Price-All-Models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7822A7-DDF6-46E7-A6AC-F61E1E7CBBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819A65C3-FC16-49A5-A0BB-3673DF9405D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{2AA7A42A-5189-4EA1-AE67-FD5CC8988654}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2AA7A42A-5189-4EA1-AE67-FD5CC8988654}"/>
   </bookViews>
   <sheets>
     <sheet name="ราคารถทั้งหมด " sheetId="1" r:id="rId1"/>
